--- a/output/asbabun nujul/book-output.xlsx
+++ b/output/asbabun nujul/book-output.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book Content" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="section" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,15 +439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,26 +457,6 @@
           <t>chapter_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>section_id</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>section_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -489,15 +467,245 @@
           <t>সূরা আল-বাক্বারাহ্</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>section_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>সূরা আল-বাক্বারাহ্</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১১৫]</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১২৫]</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৪২]</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৪৩]</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৪৪]</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৫৮]</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৮৭]</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-২:১৮৯]</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৯৫]</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>[সূরা আল-বাক্বারাহ্-০২:১৯৬]</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>content_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>section_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;[সূরা আল-বাক্বারাহ্-০২:৭৯] মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;فَوَيْلٌ لِلَّذِينَ يَكْتُبُونَ الْكِتَابَ بِأَيْدِيهِمْ ثُمَّ يَقُولُونَ هَذَا مِنْ عِنْدِ اللَّهِ لِيَشْتَرُوا بِهِ ثَمَنًا قَلِيلًا فَوَيْلٌ لَهُمْ مِمَّا كَتَبَتْ أَيْدِيهِمْ وَوَيْلٌ لَهُمْ مِمَّا يَكْسিবُونَ&lt;/ar&gt;
@@ -532,7 +740,7 @@
 &lt;p&gt;হাদীসটির বর্ণনাকারিগণ নির্ভরযোগ্য। ইবনে আবী আসেম বিশাল হাফেয। তাঁর পরিচিতি-বিবরণ রয়েছে তাযকিরাতুল হুফ্ফায (২/৬৪০) এ। আর বাকীদের রয়েছে তাহযীবুত তাহযীবে। আর হাদীসটি সহীহ (বুখারী হা/৪৫৬৬, ৬২০৭) তে শুআইব বিন আবী হামযার সুত্রে উক্ত সনদ-সহ রয়েছে। তবে সহীহতে শানে-নুযূলের কথা নেই। এমনটাই বলা হয়েছে তাফসীরে ইবনে আবী হাতেমে, যেমন রয়েছে তাফসীরে ইবনে কাসীর (১/১৩৫) এ।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>[১] তাহযীবুত তাহযীব
 [২] তিনি হলেন মুহাম্মাদ বিন আব্দুল্লাহ যুবাইরী।
@@ -544,22 +752,15 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১১৫]</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;
@@ -575,26 +776,19 @@
 &lt;p&gt;আর তিরমিযী বলেছেন, 'হাসান সহীহ হাদীস।'&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১২৫]</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;
@@ -623,26 +817,19 @@
 &lt;p&gt;তবে তাতে মাকামে ইব্রাহীম, বদর যুদ্ধের বন্দী ও পর্দার কথা উল্লেখ আছে।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৪২]</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;
@@ -669,7 +856,7 @@
 &lt;p&gt;(লুবাবুন নুকুল ফী আসবাবিন নুযূল, হাফেয সুয়ুত্বী এবং তাফসীর ইবনে কাসীর থেকে উদ্ধৃত)&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[৫] সূরা তাহরীম-৬৬:৫
 [৬] সূরা আল-বাক্বারাহ্-০২:১৪৪</t>
@@ -678,22 +865,15 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৪৩]</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;
@@ -717,7 +897,7 @@
 &lt;p&gt;আবু দাউদ ৪/৩৫৪, ত্বায়ালিসী ২/১২, হাকেম ২/২৬৯, আর তিনি বলেছেন, 'সনদ সহীহ' এবং যাহাবী তাতে স্বীকৃতি জানিয়েছেন।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>[৭] সূরা আল-বাক্বারাহ্-০২:১৪৩</t>
         </is>
@@ -725,22 +905,15 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৪৪]</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;
@@ -775,7 +948,7 @@
 &lt;p&gt;অতঃপর 'বানু সালামাহ' গোত্রের একজন ব্যক্তি পাশ দিয়ে অতিক্রম করছিলেন, এমতাবস্থায় তাঁরা সকলে ফযরের সালাতে রুকু অবস্থায় ছিলেন। এমনকি তাঁদের এক রাক'আত সালাত পড়া হয়ে গিয়েছিল তখন তাঁরা পরস্পরে আহ্বান করতে লাগল যে, কিবলা পরিবর্তন হয়েছে। তখনই সাহাবীগণ কিবলামুখী হয়ে নিজেদেরকে মুখ ফিরিয়ে নিলেন। অনুরূপ ইবনে সা'দ ৪র্থ খণ্ড ২য় ভাগে বর্ণনা করেছেন।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>[৮] সূরা আল-বাক্বারাহ্-০২:১৪২</t>
         </is>
@@ -783,22 +956,15 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৫৮]</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;ar&gt;إِنَّ الصَّفَا وَالْمَرْوَةَ مِنْ شَعَائِرِ اللهِ فَمَنْ حَجَّ الْبَيْتَ أَوِ اعْتَمَرَ فَلا جُنَاحَ عَلَيْهِ أَنْ يَطَّوَّفَ بِهِمَا&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: "নিশ্চয় 'স্বাফা' ও 'মারওয়া' (পাহাড় দু'টি) আল্লাহর নিদর্শনসমূহের অন্যতম। সুতরাং যে কা'বাগৃহের হজ্ব কিংবা উমরাহ সম্পন্ন করে, তার জন্য এই (পাহাড়) দুটি প্রদক্ষিণ (সাঈ) করলে কোন পাপ নেই। আর কোন ব্যক্তি স্বেচ্ছায় কোন পুণ্য কাজ করলে, আল্লাহ গুণগ্রাহী, সর্বজ্ঞাতা।”&lt;/meaning&gt;
@@ -815,26 +981,19 @@
 &lt;p&gt;মুসলিম (৯/২৪), তিরমিযী (৪/৭১) এ এবং তিনি সহীহ বলেছেন। আর এ কথা মেনে নিতে কোন বাধা নেই যে, আয়াতটি সকলের জন্যই অবতীর্ণ হয়েছে।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৮৭]</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;ar&gt;أُحِلَّ لَكُمْ لَيْلَةَ الصِّيَامِ الرَّفَتُ إِلَى نِسَائِكُمْ إلى قوله: وَكُلُوا وَاشْرَبُوا حَتَّى يَتَبَيَّنَ لَكُمُ الْخَيْطُ الْأَبْيَضُ مِنَ الْخَيْطِ الْأَسْوَدِ&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: "সিয়ামের রাতে তোমাদের জন্য স্ত্রী-সম্ভোগ বৈধ করা হয়েছে। তারা তোমাদের পোশাক এবং তোমরা তাদের পোশাক। আল্লাহ জানতেন যে, তোমরা আত্মপ্রতারণা করছ। তাই তো তিনি তোমাদের প্রতি সদয় হয়েছেন এবং তোমাদের অপরাধ ক্ষমা করেছেন। অতএব এখন তোমরা তোমাদের পত্নীদের সঙ্গে সহবাস করতে পার এবং আল্লাহ তোমাদের জন্য যা (সন্তান) লিখে রেখেছেন তা কামনা কর। আর তোমরা পানাহার কর; যতক্ষণ কালো সুতা (রাতের কালো রেখা) হতে ঊষার সাদা সুতা (সাদা রেখা) স্পষ্টরূপে তোমাদের নিকট প্রতিভাত না হয়।"&lt;/meaning&gt;
@@ -849,26 +1008,19 @@
 &lt;p&gt;এই আয়াত অবতীর্ণ হয়েছিল এবং ]مِنَ الْفَجْرِ[ এই অংশটি অবতীর্ণ হয়নি। ফলে কিছু লোক ছিল, তারা সিয়াম রাখার ইচ্ছা করলে, তাদের কেউ কেউ তার পায়ে সাদা ও কালো সুতো বেঁধে নিতো এবং দৃশ্যে উভয় সুতোর পার্থক্য স্পষ্ট না হওয়া পর্যন্ত খেতেই থাকত। অতঃপর অবতীর্ণ হল, ]مِنَ الْفَجْرِ[ ফলে তারা জানতে পারল যে, (কালো ও সাদা সুতো বলতে) উদ্দেশ্য, রাত ও দিন। হাদীসটিকে তাফসীর অধ্যায়ে শেষোক্ত সনদে ইবনে আবী মারয়‍্যামের হাদীস হিসাবে পুন: উদ্ধৃত করেছেন। আর এটি হল সেই বিরল হাদীসসমূহের একটি, যা তিনি কোন পরিবর্তন ছাড়াই পুন: উদ্ধৃত করেছে। হাদীসটিকে মুসলিমও (৭/২২০এ) উদ্ধৃত করেছেন।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-২:১৮৯]</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;ar&gt;وَلَيْسَ الْبِرُّ بِأَنْ تَأْتُوا الْبُيُوتَ مِنْ ظُهُورِهَا وَلَكِنَّ الْبِرَّ মَنِ اتَّقَى وَأْتُوا الْبُيُوتَ مِنْ أَبْوَابِهَا ]&lt;/ar&gt;
 &lt;meaning&gt;অর্থ: "পিছন দিক দিয়ে ঘরে প্রবেশ করা পুণ্যের কাজ নয়; কিন্তু পুণ্যের কাজ হল সংযম অবলম্বন করে চলা। অতএব তোমরা দরজাসমূহ দিয়েই ঘরে প্রবেশ কর এবং আল্লাহকে ভয় কর, তবেই তোমরা পরিত্রাণ পাবে।"&lt;/meaning&gt;
@@ -879,26 +1031,19 @@
 &lt;p&gt;আর হাকেম বলেছেন, বুখারী-মুসলিমের শর্তে হাদীসটি সহীহ এবং যাহাবী তাতে স্বীকৃতি দিয়েছেন। অথচ তাঁরা উভয়ে যা বলেছেন, তা সঠিক নয়। কারণ আবুল জাওয়াব, যার নাম আহওয়াস বিন জাওয়াব ও আম্মার বিন রুযাইক উভয়ের হাদীস বুখারী একটিও বর্ণনা করেননি, যেমন তাহযীবুত তাহযীব গ্রন্থে এ কথা বলা হয়েছে। সুতরাং হাদীসটি কেবল মুসলিমের শর্তে সহীহ।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৯৫]</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;وَأَنْفِقُوا فِي سَبِيلِ اللهِ وَلَا تُلْقُوا بِأَيْدِيكُمْ إِلَى التَّهْلُكَةِ&lt;/ar&gt;
@@ -925,26 +1070,19 @@
 &lt;p&gt;সুতরাং আয়াতটিতে সে ব্যক্তিও শামিল, যে জিহাদ ত্যাগ করে ও কার্পণ্য করে এবং সেই ব্যক্তিও শামিল, যে পাপ ক'রে ধারণা করে যে, আল্লাহ তাকে ক্ষমা করবেন না। এ কথা মেনে নিতে কোন বাধা নেই যে, সকলের জন্যই আয়াতটি অবতীর্ণ হয়েছে। আর আল্লাহই সবার চাইতে বেশি জানেন।&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>সূরা আল-বাক্বারাহ্</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>[সূরা আল-বাক্বারাহ্-০২:১৯৬]</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>&lt;div class="page-text"&gt;&lt;p&gt;মহান আল্লাহ বলেছেন,&lt;/p&gt;
 &lt;ar&gt;وَأَتِمُّوا الْحَجَّ وَالْعُمْرَةَ لِلَّهِ&lt;/ar&gt;
@@ -965,7 +1103,7 @@
 &lt;p&gt;ইমাম বুখারী তাঁর সহীহ গ্রন্থে (৪/৩৮৭তে) বলেছেন, আমাদেরকে হাদীস বর্ণনা করেছেন আবু নুআইম, তিনি বলেন, আমাদেরকে হাদীস বর্ণনা করেছেন সাইফ, তিনি বলেন, আমাকে হাদীস বর্ণনা করেছেন মুজাহিদ, তিনি বলেন, আমি আব্দুর রহমান বিন আবী লাইলার নিকট শুনেছি যে, কা'ব বিন উজরাহ (রাঃ) তাঁকে হাদীস বর্ণনা ক'রে বলেছেন যে, আমি 'হুদাইবিয়া'তে রাসূলুল্লাহ (ﷺ) এর কাছে দাঁড়ালাম। তখন আমার মাথা&lt;/p&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>[৯] মূল কপিতে হাদ্দাষানা আহমাদ ও হাদ্দাষানা মুহাম্মাদের মাঝে কিছু জায়গা সাদা আছে।
 [১০] 'খালুক' হল, জাফরান প্রভৃতি থেকে প্রস্তুত মহিলাদের ব্যবহার্য একপ্রকার সুগন্ধিদ্রব্য বিশেষ। এটি ব্যবহার করলে দেহে বা পোশাকে লালচে হলুদ রং প্রকাশ পায়।---অনুবাদক</t>
